--- a/files/nastroy-core.xlsx
+++ b/files/nastroy-core.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Блок сайта</t>
+          <t>Блок сайта (первая структура, до структуры команды)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
